--- a/results/cell_lines/glioma_cell_line_master.xlsx
+++ b/results/cell_lines/glioma_cell_line_master.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="455">
   <si>
     <t>STRIPPED_CELL_LINE_NAME</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>PRISM_AVAILABLE</t>
+  </si>
+  <si>
+    <t>PRISM_HAS_MEASUREMENTS</t>
+  </si>
+  <si>
+    <t>PRISM_NONMISSING_MEASUREMENTS</t>
   </si>
   <si>
     <t>GDSC_EXPRESSION_AVAILABLE</t>
@@ -1704,12 +1710,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R97"/>
+  <dimension ref="A1:T97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1762,28 +1768,34 @@
       <c r="R1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -1801,30 +1813,36 @@
         <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1408</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -1842,39 +1860,45 @@
         <v>1</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>190</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D4">
         <v>687588</v>
       </c>
       <c r="E4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -1894,37 +1918,43 @@
       <c r="P4" t="b">
         <v>1</v>
       </c>
-      <c r="Q4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="Q4">
+        <v>1398</v>
+      </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D5">
         <v>1240150</v>
       </c>
       <c r="E5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I5" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J5" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -1944,37 +1974,43 @@
       <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="Q5">
+        <v>190</v>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D6">
         <v>687590</v>
       </c>
       <c r="E6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -1994,37 +2030,43 @@
       <c r="P6" t="b">
         <v>1</v>
       </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="Q6">
+        <v>190</v>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D7">
         <v>906868</v>
       </c>
       <c r="E7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -2044,37 +2086,43 @@
       <c r="P7" t="b">
         <v>1</v>
       </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="Q7">
+        <v>1345</v>
+      </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D8">
         <v>906873</v>
       </c>
       <c r="E8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
@@ -2094,34 +2142,40 @@
       <c r="P8" t="b">
         <v>1</v>
       </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="Q8">
+        <v>1355</v>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I9" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J9" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -2141,28 +2195,34 @@
       <c r="P9" t="b">
         <v>0</v>
       </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F10" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -2182,37 +2242,43 @@
       <c r="P10" t="b">
         <v>0</v>
       </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D11">
         <v>687562</v>
       </c>
       <c r="E11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F11" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I11" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J11" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -2232,34 +2298,40 @@
       <c r="P11" t="b">
         <v>1</v>
       </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="Q11">
+        <v>1377</v>
+      </c>
+      <c r="R11" t="b">
+        <v>1</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F12" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J12" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
@@ -2277,39 +2349,45 @@
         <v>1</v>
       </c>
       <c r="P12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>187</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C13" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D13">
         <v>908449</v>
       </c>
       <c r="E13" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F13" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I13" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J13" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -2327,30 +2405,36 @@
         <v>0</v>
       </c>
       <c r="P13" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I14" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J14" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -2368,33 +2452,39 @@
         <v>1</v>
       </c>
       <c r="P14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>191</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H15" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="I15" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J15" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2412,39 +2502,45 @@
         <v>1</v>
       </c>
       <c r="P15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>184</v>
+      </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C16" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D16">
         <v>907271</v>
       </c>
       <c r="E16" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F16" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G16" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I16" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J16" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -2464,37 +2560,43 @@
       <c r="P16" t="b">
         <v>1</v>
       </c>
-      <c r="Q16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
+      <c r="Q16">
+        <v>1234</v>
+      </c>
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D17">
         <v>905983</v>
       </c>
       <c r="E17" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F17" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G17" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I17" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J17" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -2514,37 +2616,43 @@
       <c r="P17" t="b">
         <v>1</v>
       </c>
-      <c r="Q17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
+      <c r="Q17">
+        <v>1300</v>
+      </c>
+      <c r="R17" t="b">
+        <v>1</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C18" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D18">
         <v>906839</v>
       </c>
       <c r="E18" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F18" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G18" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I18" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J18" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -2564,37 +2672,43 @@
       <c r="P18" t="b">
         <v>1</v>
       </c>
-      <c r="Q18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17">
+      <c r="Q18">
+        <v>1360</v>
+      </c>
+      <c r="R18" t="b">
+        <v>1</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D19">
         <v>910933</v>
       </c>
       <c r="E19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F19" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G19" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I19" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J19" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -2614,37 +2728,43 @@
       <c r="P19" t="b">
         <v>1</v>
       </c>
-      <c r="Q19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="Q19">
+        <v>190</v>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D20">
         <v>905984</v>
       </c>
       <c r="E20" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F20" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I20" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J20" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
@@ -2664,28 +2784,34 @@
       <c r="P20" t="b">
         <v>1</v>
       </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17">
+      <c r="Q20">
+        <v>1351</v>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F21" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I21" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J21" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -2703,33 +2829,39 @@
         <v>1</v>
       </c>
       <c r="P21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>191</v>
+      </c>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C22" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F22" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I22" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J22" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
@@ -2747,39 +2879,45 @@
         <v>1</v>
       </c>
       <c r="P22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>1362</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D23">
         <v>687561</v>
       </c>
       <c r="E23" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F23" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G23" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I23" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J23" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -2799,28 +2937,34 @@
       <c r="P23" t="b">
         <v>1</v>
       </c>
-      <c r="Q23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17">
+      <c r="Q23">
+        <v>1344</v>
+      </c>
+      <c r="R23" t="b">
+        <v>1</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C24" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F24" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I24" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J24" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
@@ -2840,37 +2984,43 @@
       <c r="P24" t="b">
         <v>0</v>
       </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17">
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C25" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D25">
         <v>906823</v>
       </c>
       <c r="E25" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F25" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G25" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I25" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J25" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
@@ -2890,31 +3040,37 @@
       <c r="P25" t="b">
         <v>1</v>
       </c>
-      <c r="Q25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17">
+      <c r="Q25">
+        <v>1362</v>
+      </c>
+      <c r="R25" t="b">
+        <v>1</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F26" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I26" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J26" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
@@ -2932,33 +3088,39 @@
         <v>1</v>
       </c>
       <c r="P26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>1400</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C27" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F27" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G27" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I27" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J27" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
@@ -2978,37 +3140,43 @@
       <c r="P27" t="b">
         <v>0</v>
       </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C28" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D28">
         <v>905985</v>
       </c>
       <c r="E28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F28" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G28" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I28" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J28" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
@@ -3028,34 +3196,40 @@
       <c r="P28" t="b">
         <v>1</v>
       </c>
-      <c r="Q28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17">
+      <c r="Q28">
+        <v>1346</v>
+      </c>
+      <c r="R28" t="b">
+        <v>1</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D29">
         <v>907042</v>
       </c>
       <c r="E29" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F29" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I29" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J29" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
@@ -3075,37 +3249,43 @@
       <c r="P29" t="b">
         <v>1</v>
       </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17">
+      <c r="Q29">
+        <v>1327</v>
+      </c>
+      <c r="R29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D30">
         <v>909745</v>
       </c>
       <c r="E30" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F30" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I30" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J30" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
@@ -3125,31 +3305,37 @@
       <c r="P30" t="b">
         <v>1</v>
       </c>
-      <c r="Q30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17">
+      <c r="Q30">
+        <v>1440</v>
+      </c>
+      <c r="R30" t="b">
+        <v>1</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F31" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I31" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J31" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -3167,30 +3353,36 @@
         <v>1</v>
       </c>
       <c r="P31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17">
+        <v>1</v>
+      </c>
+      <c r="Q31">
+        <v>1352</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F32" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I32" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J32" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -3210,37 +3402,43 @@
       <c r="P32" t="b">
         <v>0</v>
       </c>
-      <c r="Q32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17">
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D33">
         <v>910943</v>
       </c>
       <c r="E33" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F33" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I33" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J33" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
@@ -3260,37 +3458,43 @@
       <c r="P33" t="b">
         <v>1</v>
       </c>
-      <c r="Q33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17">
+      <c r="Q33">
+        <v>148</v>
+      </c>
+      <c r="R33" t="b">
+        <v>1</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C34" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D34">
         <v>909905</v>
       </c>
       <c r="E34" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F34" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G34" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I34" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J34" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
@@ -3310,34 +3514,40 @@
       <c r="P34" t="b">
         <v>1</v>
       </c>
-      <c r="Q34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17">
+      <c r="Q34">
+        <v>1383</v>
+      </c>
+      <c r="R34" t="b">
+        <v>1</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E35" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F35" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G35" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I35" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J35" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -3355,39 +3565,45 @@
         <v>1</v>
       </c>
       <c r="P35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17">
+        <v>1</v>
+      </c>
+      <c r="Q35">
+        <v>1389</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D36">
         <v>905982</v>
       </c>
       <c r="E36" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F36" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G36" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I36" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J36" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
@@ -3407,31 +3623,37 @@
       <c r="P36" t="b">
         <v>1</v>
       </c>
-      <c r="Q36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
+      <c r="Q36">
+        <v>1356</v>
+      </c>
+      <c r="R36" t="b">
+        <v>1</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
       <c r="A37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F37" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G37" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I37" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J37" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -3449,39 +3671,45 @@
         <v>1</v>
       </c>
       <c r="P37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17">
+        <v>1</v>
+      </c>
+      <c r="Q37">
+        <v>188</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C38" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D38">
         <v>687563</v>
       </c>
       <c r="E38" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F38" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I38" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J38" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
@@ -3501,37 +3729,43 @@
       <c r="P38" t="b">
         <v>1</v>
       </c>
-      <c r="Q38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17">
+      <c r="Q38">
+        <v>1337</v>
+      </c>
+      <c r="R38" t="b">
+        <v>1</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
       <c r="A39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D39">
         <v>687592</v>
       </c>
       <c r="E39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F39" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I39" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J39" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
@@ -3551,37 +3785,43 @@
       <c r="P39" t="b">
         <v>1</v>
       </c>
-      <c r="Q39" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17">
+      <c r="Q39">
+        <v>1270</v>
+      </c>
+      <c r="R39" t="b">
+        <v>1</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D40">
         <v>687586</v>
       </c>
       <c r="E40" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F40" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I40" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J40" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
@@ -3601,28 +3841,34 @@
       <c r="P40" t="b">
         <v>1</v>
       </c>
-      <c r="Q40" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17">
+      <c r="Q40">
+        <v>1455</v>
+      </c>
+      <c r="R40" t="b">
+        <v>1</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C41" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F41" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I41" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J41" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -3642,31 +3888,37 @@
       <c r="P41" t="b">
         <v>0</v>
       </c>
-      <c r="Q41" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17">
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C42" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F42" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G42" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I42" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J42" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -3684,39 +3936,45 @@
         <v>1</v>
       </c>
       <c r="P42" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17">
+        <v>1</v>
+      </c>
+      <c r="Q42">
+        <v>1353</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19">
       <c r="A43" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B43" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C43" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D43">
         <v>1240169</v>
       </c>
       <c r="E43" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F43" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G43" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I43" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J43" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K43" t="b">
         <v>1</v>
@@ -3736,37 +3994,43 @@
       <c r="P43" t="b">
         <v>1</v>
       </c>
-      <c r="Q43" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17">
+      <c r="Q43">
+        <v>1417</v>
+      </c>
+      <c r="R43" t="b">
+        <v>1</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D44">
         <v>909712</v>
       </c>
       <c r="E44" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F44" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G44" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I44" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J44" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K44" t="b">
         <v>1</v>
@@ -3786,37 +4050,43 @@
       <c r="P44" t="b">
         <v>1</v>
       </c>
-      <c r="Q44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17">
+      <c r="Q44">
+        <v>1305</v>
+      </c>
+      <c r="R44" t="b">
+        <v>1</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C45" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D45">
         <v>907282</v>
       </c>
       <c r="E45" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F45" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I45" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J45" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K45" t="b">
         <v>1</v>
@@ -3836,34 +4106,40 @@
       <c r="P45" t="b">
         <v>1</v>
       </c>
-      <c r="Q45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17">
+      <c r="Q45">
+        <v>1421</v>
+      </c>
+      <c r="R45" t="b">
+        <v>1</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C46" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E46" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F46" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G46" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I46" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J46" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -3881,36 +4157,42 @@
         <v>1</v>
       </c>
       <c r="P46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17">
+        <v>1</v>
+      </c>
+      <c r="Q46">
+        <v>187</v>
+      </c>
+      <c r="R46" t="b">
+        <v>0</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B47" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C47" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D47">
         <v>907313</v>
       </c>
       <c r="E47" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F47" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I47" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J47" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K47" t="b">
         <v>1</v>
@@ -3930,28 +4212,34 @@
       <c r="P47" t="b">
         <v>1</v>
       </c>
-      <c r="Q47" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17">
+      <c r="Q47">
+        <v>188</v>
+      </c>
+      <c r="R47" t="b">
+        <v>1</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B48" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F48" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I48" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J48" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -3971,37 +4259,43 @@
       <c r="P48" t="b">
         <v>0</v>
       </c>
-      <c r="Q48" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17">
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48" t="b">
+        <v>0</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D49">
         <v>905986</v>
       </c>
       <c r="E49" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F49" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G49" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I49" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J49" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K49" t="b">
         <v>1</v>
@@ -4019,33 +4313,39 @@
         <v>0</v>
       </c>
       <c r="P49" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q49" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49" t="b">
+        <v>1</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F50" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H50" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I50" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J50" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -4065,37 +4365,43 @@
       <c r="P50" t="b">
         <v>0</v>
       </c>
-      <c r="Q50" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17">
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50" t="b">
+        <v>0</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B51" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C51" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D51">
         <v>687568</v>
       </c>
       <c r="E51" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F51" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="G51" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I51" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J51" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K51" t="b">
         <v>1</v>
@@ -4115,37 +4421,43 @@
       <c r="P51" t="b">
         <v>1</v>
       </c>
-      <c r="Q51" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17">
+      <c r="Q51">
+        <v>1413</v>
+      </c>
+      <c r="R51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19">
       <c r="A52" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B52" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C52" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D52">
         <v>906871</v>
       </c>
       <c r="E52" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F52" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G52" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I52" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J52" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K52" t="b">
         <v>1</v>
@@ -4165,31 +4477,37 @@
       <c r="P52" t="b">
         <v>1</v>
       </c>
-      <c r="Q52" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17">
+      <c r="Q52">
+        <v>1242</v>
+      </c>
+      <c r="R52" t="b">
+        <v>1</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19">
       <c r="A53" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C53" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E53" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F53" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I53" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J53" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K53" t="b">
         <v>0</v>
@@ -4207,33 +4525,39 @@
         <v>1</v>
       </c>
       <c r="P53" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17">
+        <v>1</v>
+      </c>
+      <c r="Q53">
+        <v>192</v>
+      </c>
+      <c r="R53" t="b">
+        <v>0</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19">
       <c r="A54" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B54" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C54" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F54" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G54" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I54" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J54" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K54" t="b">
         <v>0</v>
@@ -4253,37 +4577,43 @@
       <c r="P54" t="b">
         <v>0</v>
       </c>
-      <c r="Q54" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17">
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54" t="b">
+        <v>0</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C55" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D55">
         <v>1240168</v>
       </c>
       <c r="E55" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F55" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G55" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I55" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J55" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K55" t="b">
         <v>1</v>
@@ -4303,37 +4633,43 @@
       <c r="P55" t="b">
         <v>1</v>
       </c>
-      <c r="Q55" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17">
+      <c r="Q55">
+        <v>1364</v>
+      </c>
+      <c r="R55" t="b">
+        <v>1</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19">
       <c r="A56" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B56" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C56" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D56">
         <v>906835</v>
       </c>
       <c r="E56" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F56" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G56" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I56" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J56" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K56" t="b">
         <v>1</v>
@@ -4353,37 +4689,43 @@
       <c r="P56" t="b">
         <v>1</v>
       </c>
-      <c r="Q56" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17">
+      <c r="Q56">
+        <v>1439</v>
+      </c>
+      <c r="R56" t="b">
+        <v>1</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19">
       <c r="A57" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C57" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D57">
         <v>909750</v>
       </c>
       <c r="E57" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F57" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G57" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I57" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J57" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K57" t="b">
         <v>1</v>
@@ -4403,28 +4745,34 @@
       <c r="P57" t="b">
         <v>1</v>
       </c>
-      <c r="Q57" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17">
+      <c r="Q57">
+        <v>180</v>
+      </c>
+      <c r="R57" t="b">
+        <v>1</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19">
       <c r="A58" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B58" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C58" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F58" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I58" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J58" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K58" t="b">
         <v>0</v>
@@ -4444,31 +4792,37 @@
       <c r="P58" t="b">
         <v>0</v>
       </c>
-      <c r="Q58" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17">
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58" t="b">
+        <v>0</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19">
       <c r="A59" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E59" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F59" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I59" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J59" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
@@ -4488,37 +4842,43 @@
       <c r="P59" t="b">
         <v>0</v>
       </c>
-      <c r="Q59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17">
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59" t="b">
+        <v>0</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19">
       <c r="A60" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B60" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C60" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D60">
         <v>906746</v>
       </c>
       <c r="E60" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F60" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G60" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I60" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J60" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K60" t="b">
         <v>1</v>
@@ -4538,34 +4898,40 @@
       <c r="P60" t="b">
         <v>1</v>
       </c>
-      <c r="Q60" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17">
+      <c r="Q60">
+        <v>1377</v>
+      </c>
+      <c r="R60" t="b">
+        <v>1</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19">
       <c r="A61" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D61">
         <v>949094</v>
       </c>
       <c r="E61" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F61" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I61" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J61" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K61" t="b">
         <v>1</v>
@@ -4583,36 +4949,42 @@
         <v>0</v>
       </c>
       <c r="P61" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61" t="b">
+        <v>1</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C62" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D62">
         <v>908144</v>
       </c>
       <c r="E62" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F62" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I62" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J62" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K62" t="b">
         <v>1</v>
@@ -4630,36 +5002,42 @@
         <v>0</v>
       </c>
       <c r="P62" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62" t="b">
+        <v>1</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
       <c r="A63" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C63" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D63">
         <v>908145</v>
       </c>
       <c r="E63" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F63" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I63" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J63" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K63" t="b">
         <v>1</v>
@@ -4677,33 +5055,39 @@
         <v>0</v>
       </c>
       <c r="P63" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q63" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63" t="b">
+        <v>1</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C64" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F64" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H64" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I64" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J64" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K64" t="b">
         <v>0</v>
@@ -4723,31 +5107,37 @@
       <c r="P64" t="b">
         <v>0</v>
       </c>
-      <c r="Q64" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17">
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64" t="b">
+        <v>0</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19">
       <c r="A65" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B65" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C65" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E65" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F65" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="I65" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J65" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
@@ -4767,31 +5157,37 @@
       <c r="P65" t="b">
         <v>0</v>
       </c>
-      <c r="Q65" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17">
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65" t="b">
+        <v>0</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19">
       <c r="A66" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B66" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C66" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E66" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F66" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="I66" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J66" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K66" t="b">
         <v>0</v>
@@ -4811,28 +5207,34 @@
       <c r="P66" t="b">
         <v>0</v>
       </c>
-      <c r="Q66" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17">
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66" t="b">
+        <v>0</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19">
       <c r="A67" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C67" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F67" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="I67" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J67" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K67" t="b">
         <v>0</v>
@@ -4852,37 +5254,43 @@
       <c r="P67" t="b">
         <v>0</v>
       </c>
-      <c r="Q67" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17">
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67" t="b">
+        <v>0</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19">
       <c r="A68" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C68" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D68">
         <v>908452</v>
       </c>
       <c r="E68" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F68" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H68" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I68" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J68" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K68" t="b">
         <v>1</v>
@@ -4900,36 +5308,42 @@
         <v>0</v>
       </c>
       <c r="P68" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q68" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68" t="b">
+        <v>1</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19">
       <c r="A69" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C69" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D69">
         <v>908450</v>
       </c>
       <c r="E69" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F69" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I69" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J69" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K69" t="b">
         <v>1</v>
@@ -4947,30 +5361,36 @@
         <v>0</v>
       </c>
       <c r="P69" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q69" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69" t="b">
+        <v>1</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19">
       <c r="A70" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F70" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I70" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J70" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K70" t="b">
         <v>0</v>
@@ -4990,28 +5410,34 @@
       <c r="P70" t="b">
         <v>0</v>
       </c>
-      <c r="Q70" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17">
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70" t="b">
+        <v>0</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19">
       <c r="A71" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C71" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F71" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I71" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J71" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>
@@ -5031,28 +5457,34 @@
       <c r="P71" t="b">
         <v>0</v>
       </c>
-      <c r="Q71" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17">
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71" t="b">
+        <v>0</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19">
       <c r="A72" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F72" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="I72" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J72" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K72" t="b">
         <v>0</v>
@@ -5072,28 +5504,34 @@
       <c r="P72" t="b">
         <v>0</v>
       </c>
-      <c r="Q72" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17">
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72" t="b">
+        <v>0</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19">
       <c r="A73" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B73" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F73" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="I73" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J73" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K73" t="b">
         <v>0</v>
@@ -5113,28 +5551,34 @@
       <c r="P73" t="b">
         <v>0</v>
       </c>
-      <c r="Q73" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17">
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73" t="b">
+        <v>0</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19">
       <c r="A74" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B74" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F74" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I74" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J74" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K74" t="b">
         <v>0</v>
@@ -5154,28 +5598,34 @@
       <c r="P74" t="b">
         <v>0</v>
       </c>
-      <c r="Q74" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17">
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74" t="b">
+        <v>0</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19">
       <c r="A75" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C75" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F75" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I75" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J75" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K75" t="b">
         <v>0</v>
@@ -5195,28 +5645,34 @@
       <c r="P75" t="b">
         <v>0</v>
       </c>
-      <c r="Q75" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17">
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75" t="b">
+        <v>0</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19">
       <c r="A76" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C76" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F76" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="I76" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J76" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K76" t="b">
         <v>0</v>
@@ -5236,34 +5692,40 @@
       <c r="P76" t="b">
         <v>0</v>
       </c>
-      <c r="Q76" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17">
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76" t="b">
+        <v>0</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19">
       <c r="A77" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B77" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C77" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D77">
         <v>946366</v>
       </c>
       <c r="E77" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F77" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="I77" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J77" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K77" t="b">
         <v>0</v>
@@ -5283,34 +5745,40 @@
       <c r="P77" t="b">
         <v>0</v>
       </c>
-      <c r="Q77" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17">
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77" t="b">
+        <v>0</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
       <c r="A78" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B78" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C78" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D78">
         <v>946367</v>
       </c>
       <c r="E78" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F78" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I78" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J78" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K78" t="b">
         <v>1</v>
@@ -5328,36 +5796,42 @@
         <v>0</v>
       </c>
       <c r="P78" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q78" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78" t="b">
+        <v>1</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B79" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C79" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D79">
         <v>946368</v>
       </c>
       <c r="E79" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F79" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I79" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J79" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K79" t="b">
         <v>1</v>
@@ -5375,36 +5849,42 @@
         <v>0</v>
       </c>
       <c r="P79" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79" t="b">
+        <v>1</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19">
       <c r="A80" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B80" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C80" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D80">
         <v>946369</v>
       </c>
       <c r="E80" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F80" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="I80" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J80" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K80" t="b">
         <v>1</v>
@@ -5422,36 +5902,42 @@
         <v>0</v>
       </c>
       <c r="P80" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80" t="b">
+        <v>1</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19">
       <c r="A81" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B81" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C81" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D81">
         <v>946370</v>
       </c>
       <c r="E81" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F81" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="I81" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J81" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K81" t="b">
         <v>1</v>
@@ -5469,36 +5955,42 @@
         <v>0</v>
       </c>
       <c r="P81" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q81" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81" t="b">
+        <v>1</v>
+      </c>
+      <c r="S81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19">
       <c r="A82" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B82" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C82" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D82">
         <v>946372</v>
       </c>
       <c r="E82" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F82" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="I82" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J82" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K82" t="b">
         <v>1</v>
@@ -5516,36 +6008,42 @@
         <v>0</v>
       </c>
       <c r="P82" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q82" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82" t="b">
+        <v>1</v>
+      </c>
+      <c r="S82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19">
       <c r="A83" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C83" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D83">
         <v>946373</v>
       </c>
       <c r="E83" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F83" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I83" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J83" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K83" t="b">
         <v>1</v>
@@ -5563,36 +6061,42 @@
         <v>0</v>
       </c>
       <c r="P83" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q83" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83" t="b">
+        <v>1</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19">
       <c r="A84" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B84" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C84" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D84">
         <v>753549</v>
       </c>
       <c r="E84" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F84" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="I84" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J84" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K84" t="b">
         <v>1</v>
@@ -5610,36 +6114,42 @@
         <v>0</v>
       </c>
       <c r="P84" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84" t="b">
+        <v>1</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19">
       <c r="A85" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B85" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C85" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D85">
         <v>946377</v>
       </c>
       <c r="E85" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F85" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="I85" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J85" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K85" t="b">
         <v>1</v>
@@ -5657,36 +6167,42 @@
         <v>0</v>
       </c>
       <c r="P85" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q85" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85" t="b">
+        <v>1</v>
+      </c>
+      <c r="S85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19">
       <c r="A86" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B86" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C86" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D86">
         <v>907279</v>
       </c>
       <c r="E86" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F86" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="I86" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J86" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K86" t="b">
         <v>1</v>
@@ -5704,36 +6220,42 @@
         <v>0</v>
       </c>
       <c r="P86" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86" t="b">
+        <v>1</v>
+      </c>
+      <c r="S86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19">
       <c r="A87" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B87" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C87" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D87">
         <v>924188</v>
       </c>
       <c r="E87" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F87" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I87" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J87" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K87" t="b">
         <v>1</v>
@@ -5751,36 +6273,42 @@
         <v>0</v>
       </c>
       <c r="P87" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q87" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87" t="b">
+        <v>1</v>
+      </c>
+      <c r="S87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19">
       <c r="A88" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B88" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C88" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D88">
         <v>910694</v>
       </c>
       <c r="E88" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F88" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="I88" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J88" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K88" t="b">
         <v>1</v>
@@ -5798,36 +6326,42 @@
         <v>0</v>
       </c>
       <c r="P88" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q88" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88" t="b">
+        <v>1</v>
+      </c>
+      <c r="S88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19">
       <c r="A89" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B89" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C89" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D89">
         <v>1240170</v>
       </c>
       <c r="E89" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F89" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I89" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J89" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K89" t="b">
         <v>1</v>
@@ -5845,83 +6379,95 @@
         <v>0</v>
       </c>
       <c r="P89" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q89" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89" t="b">
+        <v>1</v>
+      </c>
+      <c r="S89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19">
       <c r="A90" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B90" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C90" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D90">
         <v>909729</v>
       </c>
       <c r="E90" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F90" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="I90" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J90" t="s">
+        <v>452</v>
+      </c>
+      <c r="K90" t="b">
+        <v>1</v>
+      </c>
+      <c r="L90" t="b">
+        <v>1</v>
+      </c>
+      <c r="M90" t="b">
+        <v>0</v>
+      </c>
+      <c r="N90" t="b">
+        <v>0</v>
+      </c>
+      <c r="O90" t="b">
+        <v>0</v>
+      </c>
+      <c r="P90" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="R90" t="b">
+        <v>1</v>
+      </c>
+      <c r="S90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19">
+      <c r="A91" t="s">
+        <v>109</v>
+      </c>
+      <c r="B91" t="s">
+        <v>188</v>
+      </c>
+      <c r="C91" t="s">
+        <v>282</v>
+      </c>
+      <c r="E91" t="s">
+        <v>350</v>
+      </c>
+      <c r="F91" t="s">
+        <v>440</v>
+      </c>
+      <c r="H91" t="s">
         <v>450</v>
       </c>
-      <c r="K90" t="b">
-        <v>1</v>
-      </c>
-      <c r="L90" t="b">
-        <v>1</v>
-      </c>
-      <c r="M90" t="b">
-        <v>0</v>
-      </c>
-      <c r="N90" t="b">
-        <v>0</v>
-      </c>
-      <c r="O90" t="b">
-        <v>0</v>
-      </c>
-      <c r="P90" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q90" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17">
-      <c r="A91" t="s">
-        <v>107</v>
-      </c>
-      <c r="B91" t="s">
-        <v>186</v>
-      </c>
-      <c r="C91" t="s">
-        <v>280</v>
-      </c>
-      <c r="E91" t="s">
-        <v>348</v>
-      </c>
-      <c r="F91" t="s">
-        <v>438</v>
-      </c>
-      <c r="H91" t="s">
-        <v>448</v>
-      </c>
       <c r="I91" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J91" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K91" t="b">
         <v>0</v>
@@ -5941,28 +6487,34 @@
       <c r="P91" t="b">
         <v>0</v>
       </c>
-      <c r="Q91" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17">
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="R91" t="b">
+        <v>0</v>
+      </c>
+      <c r="S91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19">
       <c r="A92" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B92" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C92" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F92" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="I92" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J92" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K92" t="b">
         <v>0</v>
@@ -5982,28 +6534,34 @@
       <c r="P92" t="b">
         <v>0</v>
       </c>
-      <c r="Q92" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17">
+      <c r="Q92">
+        <v>0</v>
+      </c>
+      <c r="R92" t="b">
+        <v>0</v>
+      </c>
+      <c r="S92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19">
       <c r="A93" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B93" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C93" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F93" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I93" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J93" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K93" t="b">
         <v>0</v>
@@ -6023,28 +6581,34 @@
       <c r="P93" t="b">
         <v>0</v>
       </c>
-      <c r="Q93" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17">
+      <c r="Q93">
+        <v>0</v>
+      </c>
+      <c r="R93" t="b">
+        <v>0</v>
+      </c>
+      <c r="S93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19">
       <c r="A94" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C94" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F94" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I94" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J94" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K94" t="b">
         <v>0</v>
@@ -6064,28 +6628,34 @@
       <c r="P94" t="b">
         <v>0</v>
       </c>
-      <c r="Q94" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17">
+      <c r="Q94">
+        <v>0</v>
+      </c>
+      <c r="R94" t="b">
+        <v>0</v>
+      </c>
+      <c r="S94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19">
       <c r="A95" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B95" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C95" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F95" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="I95" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J95" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K95" t="b">
         <v>0</v>
@@ -6105,28 +6675,34 @@
       <c r="P95" t="b">
         <v>0</v>
       </c>
-      <c r="Q95" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17">
+      <c r="Q95">
+        <v>0</v>
+      </c>
+      <c r="R95" t="b">
+        <v>0</v>
+      </c>
+      <c r="S95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19">
       <c r="A96" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B96" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C96" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F96" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="I96" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J96" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K96" t="b">
         <v>0</v>
@@ -6146,25 +6722,31 @@
       <c r="P96" t="b">
         <v>0</v>
       </c>
-      <c r="Q96" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17">
+      <c r="Q96">
+        <v>0</v>
+      </c>
+      <c r="R96" t="b">
+        <v>0</v>
+      </c>
+      <c r="S96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19">
       <c r="A97" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B97" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C97" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I97" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J97" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K97" t="b">
         <v>0</v>
@@ -6184,7 +6766,13 @@
       <c r="P97" t="b">
         <v>0</v>
       </c>
-      <c r="Q97" t="b">
+      <c r="Q97">
+        <v>0</v>
+      </c>
+      <c r="R97" t="b">
+        <v>0</v>
+      </c>
+      <c r="S97" t="b">
         <v>1</v>
       </c>
     </row>
